--- a/questionnaire_templates/039_wioa_monthly_check_in--questionnaire_templates.xlsx
+++ b/questionnaire_templates/039_wioa_monthly_check_in--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'location_option_1',_'label':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'location_option_1', 'label': 'Location 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'location_option_2',_'label':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'location_option_2', 'label': 'Location 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'location_option_3',_'label':_'location_3'}</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'location_option_3', 'label': 'Location 3'}</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'comments_option_1',_'label':_'comments_1'}</t>
+          <t>comments_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'comments_option_1', 'label': 'Comments 1'}</t>
+          <t>Comments 1</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'comments_option_2',_'label':_'comments_2'}</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'comments_option_2', 'label': 'Comments 2'}</t>
+          <t>Comments 2</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'assigned_tool_option_1',_'label':_'tool_1'}</t>
+          <t>tool_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'assigned_tool_option_1', 'label': 'Tool 1'}</t>
+          <t>Tool 1</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'assigned_tool_option_2',_'label':_'tool_2'}</t>
+          <t>tool_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'assigned_tool_option_2', 'label': 'Tool 2'}</t>
+          <t>Tool 2</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'category_option_1',_'label':_'category_1'}</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'category_option_1', 'label': 'Category 1'}</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'category_option_2',_'label':_'category_2'}</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'category_option_2', 'label': 'Category 2'}</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'category_option_3',_'label':_'category_3'}</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'category_option_3', 'label': 'Category 3'}</t>
+          <t>Category 3</t>
         </is>
       </c>
     </row>
